--- a/public/upload/export_excel/รายงานจองรายเดือน_08-2025.xlsx
+++ b/public/upload/export_excel/รายงานจองรายเดือน_08-2025.xlsx
@@ -15,7 +15,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" uniqueCount="27">
   <si>
     <t>ห้อง</t>
   </si>
@@ -75,6 +75,27 @@
   </si>
   <si>
     <t>A103</t>
+  </si>
+  <si>
+    <t>A104</t>
+  </si>
+  <si>
+    <t>A105</t>
+  </si>
+  <si>
+    <t>A106</t>
+  </si>
+  <si>
+    <t>A107</t>
+  </si>
+  <si>
+    <t>A201</t>
+  </si>
+  <si>
+    <t>A205</t>
+  </si>
+  <si>
+    <t>A108</t>
   </si>
 </sst>
 </file>
@@ -441,7 +462,7 @@
   <sheetPr>
     <outlinePr summaryBelow="1" summaryRight="1"/>
   </sheetPr>
-  <dimension ref="A1:O7"/>
+  <dimension ref="A1:O17"/>
   <sheetFormatPr defaultRowHeight="14.4" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col min="1" max="1" width="8.141" bestFit="true" customWidth="true" style="0"/>
@@ -544,32 +565,29 @@
         <v>104</v>
       </c>
       <c r="D3">
-        <v>360</v>
+        <v>696</v>
       </c>
     </row>
     <row r="4" spans="1:15">
       <c r="A4" t="s">
-        <v>17</v>
+        <v>18</v>
       </c>
       <c r="B4">
         <v>5000</v>
       </c>
-      <c r="C4">
-        <v>104</v>
-      </c>
       <c r="D4">
-        <v>360</v>
+        <v>455</v>
       </c>
     </row>
     <row r="5" spans="1:15">
       <c r="A5" t="s">
-        <v>18</v>
+        <v>19</v>
       </c>
       <c r="B5">
         <v>5000</v>
       </c>
       <c r="D5">
-        <v>455</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="6" spans="1:15">
@@ -585,13 +603,108 @@
     </row>
     <row r="7" spans="1:15">
       <c r="A7" t="s">
-        <v>19</v>
+        <v>20</v>
       </c>
       <c r="B7">
         <v>5000</v>
       </c>
       <c r="D7">
-        <v>1032</v>
+        <v>320</v>
+      </c>
+    </row>
+    <row r="8" spans="1:15">
+      <c r="A8" t="s">
+        <v>21</v>
+      </c>
+      <c r="B8">
+        <v>5000</v>
+      </c>
+      <c r="D8">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="9" spans="1:15">
+      <c r="A9" t="s">
+        <v>21</v>
+      </c>
+      <c r="B9">
+        <v>5000</v>
+      </c>
+      <c r="D9">
+        <v>49</v>
+      </c>
+    </row>
+    <row r="10" spans="1:15">
+      <c r="A10" t="s">
+        <v>22</v>
+      </c>
+      <c r="B10">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="11" spans="1:15">
+      <c r="A11" t="s">
+        <v>22</v>
+      </c>
+      <c r="B11">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="12" spans="1:15">
+      <c r="A12" t="s">
+        <v>23</v>
+      </c>
+      <c r="B12">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="13" spans="1:15">
+      <c r="A13" t="s">
+        <v>23</v>
+      </c>
+      <c r="B13">
+        <v>5000</v>
+      </c>
+    </row>
+    <row r="14" spans="1:15">
+      <c r="A14" t="s">
+        <v>24</v>
+      </c>
+      <c r="B14">
+        <v>3000</v>
+      </c>
+      <c r="D14">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="15" spans="1:15">
+      <c r="A15" t="s">
+        <v>24</v>
+      </c>
+      <c r="B15">
+        <v>3000</v>
+      </c>
+      <c r="D15">
+        <v>672</v>
+      </c>
+    </row>
+    <row r="16" spans="1:15">
+      <c r="A16" t="s">
+        <v>25</v>
+      </c>
+      <c r="B16">
+        <v>3000</v>
+      </c>
+      <c r="D16">
+        <v>238</v>
+      </c>
+    </row>
+    <row r="17" spans="1:15">
+      <c r="A17" t="s">
+        <v>26</v>
+      </c>
+      <c r="B17">
+        <v>5000</v>
       </c>
     </row>
   </sheetData>
